--- a/docs/smeta.xlsx
+++ b/docs/smeta.xlsx
@@ -718,19 +718,19 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Отверстия, 2 шт</t>
+          <t>Отверстия</t>
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>19000</v>
+        <v>9500</v>
       </c>
       <c r="F17" s="9">
         <f>IF(OR(C17="",E17=""),"",C17*E17)</f>

--- a/docs/smeta.xlsx
+++ b/docs/smeta.xlsx
@@ -659,7 +659,7 @@
       </c>
       <c r="F14" s="9">
         <f>IF(OR(C14="",E14=""),"",C14*E14)</f>
-        <v/>
+        <v>49950</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
@@ -684,7 +684,7 @@
       </c>
       <c r="F15" s="9">
         <f>IF(OR(C15="",E15=""),"",C15*E15)</f>
-        <v/>
+        <v>49000</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1">
@@ -709,7 +709,7 @@
       </c>
       <c r="F16" s="9">
         <f>IF(OR(C16="",E16=""),"",C16*E16)</f>
-        <v/>
+        <v>13000</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
@@ -734,7 +734,7 @@
       </c>
       <c r="F17" s="9">
         <f>IF(OR(C17="",E17=""),"",C17*E17)</f>
-        <v/>
+        <v>19000</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
@@ -759,7 +759,7 @@
       </c>
       <c r="F18" s="9">
         <f>IF(OR(C18="",E18=""),"",C18*E18)</f>
-        <v/>
+        <v>16000</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
@@ -784,7 +784,7 @@
       </c>
       <c r="F19" s="9">
         <f>IF(OR(C19="",E19=""),"",C19*E19)</f>
-        <v/>
+        <v>18000</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
@@ -809,7 +809,7 @@
       </c>
       <c r="F20" s="9">
         <f>IF(OR(C20="",E20=""),"",C20*E20)</f>
-        <v/>
+        <v>7000</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
@@ -820,7 +820,7 @@
       <c r="C21" s="7" t="n"/>
       <c r="D21" s="7" t="n"/>
       <c r="E21" s="9" t="n"/>
-      <c r="F21" s="9">
+      <c r="F21" s="9" t="str">
         <f>IF(OR(C21="",E21=""),"",C21*E21)</f>
         <v/>
       </c>
@@ -833,7 +833,7 @@
       <c r="C22" s="7" t="n"/>
       <c r="D22" s="7" t="n"/>
       <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9">
+      <c r="F22" s="9" t="str">
         <f>IF(OR(C22="",E22=""),"",C22*E22)</f>
         <v/>
       </c>
@@ -846,7 +846,7 @@
       <c r="C23" s="7" t="n"/>
       <c r="D23" s="7" t="n"/>
       <c r="E23" s="9" t="n"/>
-      <c r="F23" s="9">
+      <c r="F23" s="9" t="str">
         <f>IF(OR(C23="",E23=""),"",C23*E23)</f>
         <v/>
       </c>
@@ -859,7 +859,7 @@
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="9" t="n"/>
-      <c r="F24" s="9">
+      <c r="F24" s="9" t="str">
         <f>IF(OR(C24="",E24=""),"",C24*E24)</f>
         <v/>
       </c>
@@ -872,7 +872,7 @@
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="9" t="n"/>
-      <c r="F25" s="9">
+      <c r="F25" s="9" t="str">
         <f>IF(OR(C25="",E25=""),"",C25*E25)</f>
         <v/>
       </c>
@@ -885,7 +885,7 @@
       <c r="C26" s="7" t="n"/>
       <c r="D26" s="7" t="n"/>
       <c r="E26" s="9" t="n"/>
-      <c r="F26" s="9">
+      <c r="F26" s="9" t="str">
         <f>IF(OR(C26="",E26=""),"",C26*E26)</f>
         <v/>
       </c>
@@ -898,7 +898,7 @@
       <c r="C27" s="7" t="n"/>
       <c r="D27" s="7" t="n"/>
       <c r="E27" s="9" t="n"/>
-      <c r="F27" s="9">
+      <c r="F27" s="9" t="str">
         <f>IF(OR(C27="",E27=""),"",C27*E27)</f>
         <v/>
       </c>
@@ -911,7 +911,7 @@
       <c r="C28" s="7" t="n"/>
       <c r="D28" s="7" t="n"/>
       <c r="E28" s="9" t="n"/>
-      <c r="F28" s="9">
+      <c r="F28" s="9" t="str">
         <f>IF(OR(C28="",E28=""),"",C28*E28)</f>
         <v/>
       </c>
@@ -924,7 +924,7 @@
       </c>
       <c r="F29" s="11">
         <f>SUM(F14:F28)</f>
-        <v/>
+        <v>171950</v>
       </c>
     </row>
     <row r="31">
